--- a/survey_templates/041_school_pastoral_care_survey--survey_templates.xlsx
+++ b/survey_templates/041_school_pastoral_care_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Staff Feedback Frequency</t>
+          <t>Staff Feedback Frequency (2)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Student Feedback Frequency</t>
+          <t>Student Feedback Frequency Frequency</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parent Feedback Frequency</t>
+          <t>Parent Feedback Frequency Frequency</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Staff Feedback Frequency</t>
+          <t>Staff Feedback Frequency Frequency</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1029,12 +1029,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1232,29 +1232,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>student_support_frequency_choices</t>
+          <t>parent_support_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1266,216 +1266,301 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>staff_feedback_frequency_choices</t>
+          <t>student_support_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>staff_feedback_frequency_choices</t>
+          <t>student_support_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>student_feedback_frequency_frequency_choices</t>
+          <t>staff_feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>student_feedback_frequency_frequency_choices</t>
+          <t>staff_feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>student_feedback_frequency_frequency_choices</t>
+          <t>staff_feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>parent_feedback_frequency_frequency_choices</t>
+          <t>student_feedback_frequency_frequency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>parent_feedback_frequency_frequency_choices</t>
+          <t>student_feedback_frequency_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>staff_feedback_frequency_frequency_choices</t>
+          <t>student_feedback_frequency_frequency_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>staff_feedback_frequency_frequency_choices</t>
+          <t>parent_feedback_frequency_frequency_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>staff_feedback_frequency_frequency_choices</t>
+          <t>parent_feedback_frequency_frequency_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>wellbeing_support_frequency_choices</t>
+          <t>parent_feedback_frequency_frequency_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>staff_feedback_frequency_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>staff_feedback_frequency_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>staff_feedback_frequency_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>wellbeing_support_frequency_choices</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Option 2</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>wellbeing_support_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>wellbeing_support_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
